--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Git\deep_learning_team_project_data_pre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67CF810-404C-4492-BFF8-C51EF99CC95C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CA896D-DBEC-47FE-A8DD-9EB48ADB6FB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -147,28 +147,58 @@
     <t>데이터셋 여부</t>
   </si>
   <si>
-    <t>있음 - 서울 열린데이터광장(따릉이, 지하철/버스 승하차), 기상청 기상자료개방포털, 공공데이터포털 전력소비량</t>
-  </si>
-  <si>
-    <t>있음 - MVTec AD(표준 벤치마크), Kaggle 안전모 착용탐지, AI허브 산업단지 열화상(약 103만 장)</t>
-  </si>
-  <si>
-    <t>있음 - URFD·Le2i(해외, 즉시), AI허브 낙상사고 위험동작 영상-센서쌍(승인 필요)</t>
-  </si>
-  <si>
-    <t>있음 - AI허브 도로 노면결함·포트홀 이미지(승인 필요), Kaggle pothole detection(즉시)</t>
-  </si>
-  <si>
-    <t>있음(문서 수집형) - 공공데이터포털, 국가법령정보센터, 복지로 등 정책 문서</t>
-  </si>
-  <si>
-    <t>실외기 전용 데이터 없음 - AI허브 산업단지 열화상(승인 필요), Kaggle 태양광 열화상(즉시)으로 대체</t>
-  </si>
-  <si>
-    <t>이동 이벤트 데이터는 공개(장애인콜택시 탑승내역 등, 서울시설공단/공공데이터포털). 단 장애유형·정도 결합 데이터는 비공개</t>
-  </si>
-  <si>
-    <t>부분적 - 모듈2(작물 병해 이미지)는 AI허브 '노지 작물 질병/해충 진단 이미지'(35만~50만 건, 승인 필요), DACON 대안 존재. 모듈1은 위험지수 라벨 직접 설계 필요. 모듈3은 데이터 없음</t>
+    <t>있음 - 서울 열린데이터광장(따릉이, 지하철/버스 승하차), 기상청 기상자료개방포털, 공공데이터포털 전력소비량
+[데이터셋 링크]
+- 따릉이 대여이력: https://data.seoul.go.kr/dataList/OA-15182/F/1/datasetView.do
+- 지하철 승하차인원: https://data.seoul.go.kr/dataList/OA-12252/S/1/datasetView.do
+- 버스 승하차인원: https://data.seoul.go.kr/dataList/OA-12912/S/1/datasetView.do
+- 기상자료개방포털: https://data.kma.go.kr/
+- 전력사용량(지역별·용도별): https://www.data.go.kr/data/15031941/fileData.do</t>
+  </si>
+  <si>
+    <t>있음 - MVTec AD(표준 벤치마크), Kaggle 안전모 착용탐지, AI허브 산업단지 열화상(약 103만 장)
+[데이터셋 링크]
+- MVTec AD: https://www.mvtec.com/research-teaching/datasets/mvtec-ad
+- Kaggle 안전모 착용탐지: https://www.kaggle.com/datasets/andrewmvd/hard-hat-detection
+- AI허브 열화상카메라이미지(산업단지): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=235</t>
+  </si>
+  <si>
+    <t>있음 - URFD·Le2i(해외, 즉시), AI허브 낙상사고 위험동작 영상-센서쌍(승인 필요)
+[데이터셋 링크]
+- URFD(공식): http://fenix.univ.rzeszow.pl/mkepski/ds/uf.html
+- Le2i(Kaggle 미러, 원본 접속불가): https://www.kaggle.com/datasets/tuyenldvn/falldataset-imvia
+- AI허브 낙상사고 위험동작 영상-센서: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=71641</t>
+  </si>
+  <si>
+    <t>있음 - AI허브 도로 노면결함·포트홀 이미지(승인 필요), Kaggle pothole detection(즉시)
+[데이터셋 링크]
+- AI허브 고해상도 도로노면 이미지: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=71781
+- AI허브 보행안전 도로시설물: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
+- Kaggle Pothole Detection(즉시): https://www.kaggle.com/datasets/andrewmvd/pothole-detection</t>
+  </si>
+  <si>
+    <t>있음(문서 수집형) - 공공데이터포털, 국가법령정보센터, 복지로 등 정책 문서
+[데이터셋 링크]
+- 공공데이터포털: https://www.data.go.kr/
+- 국가법령정보 공동활용 Open API: https://open.law.go.kr/LSO/main.do
+- 복지로: https://www.bokjiro.go.kr/</t>
+  </si>
+  <si>
+    <t>이동 이벤트 데이터는 공개(장애인콜택시 탑승내역 등, 서울시설공단/공공데이터포털). 단 장애유형·정도 결합 데이터는 비공개
+[데이터셋 링크]
+- 장애인콜택시 탑승내역: https://www.data.go.kr/data/15115859/fileData.do
+- 장애인콜택시 일별이용현황: https://data.seoul.go.kr/dataList/OA-13550/L/1/datasetView.do
+- 장애인콜시스템정보: https://data.seoul.go.kr/dataList/OA-15558/A/1/datasetView.do
+- 교통약자이동지원센터표준데이터: https://www.data.go.kr/data/15028207/standard.do</t>
+  </si>
+  <si>
+    <t>부분적 - 모듈2(작물 병해 이미지)는 AI허브 '노지 작물 질병/해충 진단 이미지'(35만~50만 건, 승인 필요), DACON 대안 존재. 모듈1은 위험지수 라벨 직접 설계 필요. 모듈3은 데이터 없음
+[데이터셋 링크]
+- (모듈2) AI허브 노지작물 질병진단 이미지: https://aihub.or.kr/aidata/30731
+- (모듈2) AI허브 노지작물 해충진단 이미지: https://aihub.or.kr/aihubdata/data/view.do?dataSetSn=148
+- (모듈2 대안) DACON 작물병해진단 AI 경진대회: https://dacon.io/competitions/official/235870/data
+- (모듈1) 기상자료개방포털: https://data.kma.go.kr/
+- (모듈3, 데이터 없음 → 대체) Autonomous Greenhouse Challenge(관수/기후제어 시계열): https://data.4tu.nl/articles/_/12764777/2</t>
   </si>
   <si>
     <t>데이터 확보 난이도</t>
@@ -268,13 +298,632 @@
   </si>
   <si>
     <t>보유 중인 기상청 폭염데이터(2019~2026, 약 200개 지점 일별)로 모듈1 보조 가능</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허브</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>산업단지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>승인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), Kaggle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>태양광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열화상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>즉시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">대체
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터셋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>링크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>] (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전용은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보완</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+- AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>허브</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>열화상카메라이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>객체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에어컨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실외기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포함되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>승인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=235
+- Kaggle Thermal Solar PV Anomaly(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>즉시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>): https://www.kaggle.com/datasets/pkdarabi/solarpanel
+- Kaggle Photovoltaic System Thermography: https://www.kaggle.com/datasets/marcosgabriel/photovoltaic-system-thermography</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +958,23 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="6">
@@ -370,7 +1036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,6 +1058,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,7 +1432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="33.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -850,7 +1519,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="339.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -869,130 +1538,130 @@
       <c r="F6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="4" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="G8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -522,13 +522,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="9"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -582,6 +585,21 @@
           <t>9 (1+7 결합)</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10 (CV: 보행 접근성 매핑)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>11 (고령 보행자 사고위험 예측)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>12 (이동약자 정책 RAG)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -618,6 +636,21 @@
           <t>9 (1+7 결합)</t>
         </is>
       </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>10 (CV: 보행 접근성 매핑)</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>11 (고령 보행자 사고위험 예측)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>12 (이동약자 정책 RAG)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -679,6 +712,22 @@
 (1순위 + 7순위 결합)</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>보행로 접근성 시설물 자동 탐지 및 매핑 서비스
+(이동약자 데이터에서 파생, CV)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>고령 보행자 교통사고 위험 예측 및 인프라 우선순위 분석</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>이동약자 정책·복지 제도 Q&amp;A RAG 서비스</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="54.95" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -731,6 +780,21 @@
           <t>Time-Series + 정책분석(형평성)</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Computer Vision / 공간AI</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Time-Series/Tabular + 공간분석</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>NLP / RAG</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="95.09999999999999" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -781,6 +845,21 @@
       <c r="J5" s="4" t="inlineStr">
         <is>
           <t>TFT, PatchTST, N-BEATS, XGBoost/LightGBM 비교, SHAP (1순위 기법을 콜택시 수요예측에 적용)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>YOLOv8/v11 객체탐지 또는 SAM 세그멘테이션(턱낮춤·점자블록·계단/장애물 탐지), 좌표 매핑 후 접근성 점수화, Folium/Streamlit 지도</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>TabNet 또는 지역 그래프 기반 GNN, XGBoost 베이스라인 비교, SHAP 해석</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>LangChain/LlamaIndex, BGE-m3 임베딩, Hybrid Search(FAISS/Qdrant), 한국어 sLLM, RAGAS</t>
         </is>
       </c>
     </row>
@@ -877,6 +956,30 @@
 - 기상자료개방포털: https://data.kma.go.kr/</t>
         </is>
       </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>있음(부분) - AI허브 '보행 안전을 위한 도로 시설물 데이터'(약 102.5만 장, 안전·관리·환경·편의시설 유형별 양호/불량 판정, 턱낮춤·점자블록 포함, 승인 필요)
+[데이터셋 링크]
+- AI허브 보행 안전을 위한 도로 시설물 데이터: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
+- AI허브 1인칭 시점 보행영상(보조자료): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=159</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>부분적 - TAAS(도로교통공단 교통사고분석시스템)에서 지역별·연령별 사고통계 조회 가능(대량 다운로드는 번거로움), 노인복지시설 위치는 공공데이터포털에서 확보 가능. PSI 지표 원자료 공개 여부는 미확인 → 직접 위험지수를 설계해야 할 가능성이 높음
+[데이터셋 링크]
+- TAAS 교통사고분석시스템: https://taas.koroad.or.kr/
+- 보건복지부 노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>있음(문서 수집형) - 국가법령정보 공동활용 API(교통약자의 이동편의 증진법 등), 복지로, '이동약자_대중교통_국내외비교_보고서.docx' 자체도 코퍼스로 활용 가능
+[데이터셋 링크]
+- 국가법령정보 공동활용 Open API: https://open.law.go.kr/LSO/main.do
+- 복지로: https://www.bokjiro.go.kr/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -929,6 +1032,21 @@
           <t>즉시 다운로드 (승인 절차 없음, 1순위·7순위 데이터 그대로 재사용)</t>
         </is>
       </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>AI허브 승인 필요 - 대기시간이 2일 일정에 리스크. 승인 지연 시 Roboflow/Kaggle의 sidewalk·curb-ramp 데이터로 즉시 대체 검증 필요(별도 확인 필요)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>혼재 - TAAS는 웹 통계 조회 중심이라 벌크 다운로드가 번거로움. PSI 원자료 미확인은 추가 리스크</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>즉시 수집 가능 (라벨링 불필요, 문서 수집형 과제)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -981,6 +1099,21 @@
           <t>상 - 1순위 파이프라인 재사용</t>
         </is>
       </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>하 (데이터 확보·가공에 시간이 걸릴 가능성 높음)</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1033,6 +1166,21 @@
           <t>통계/ML 대비 딥러닝 시계열 성능 비교(RMSE·MAE) + XAI 해석에 이동약자 수요예측이라는 사회적 임팩트까지 결합 - 기술력과 서사를 동시에 어필</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>단순 mAP 개선이 아니라 '접근성 점수화' 로직 설계 + GIS 대시보드로 실무형 결과물. 보고서에서 확인된 '전용 앱 정보가 부정확하다'는 실제 문제(머니투데이 2024.10.15)를 기술로 보완하는 서사</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>정형 데이터에서 딥러닝이 통계모델보다 실제로 나은지 비교검증 + 위험 인프라 우선순위 정책 제언까지 연결</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid Search·Re-ranking·환각 방지 정량평가로 RAG 트렌드 적합성 입증, '내가 받을 수 있는 지원제도 찾기'라는 실사용 시나리오가 명확</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1083,6 +1231,21 @@
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>콜택시 데이터가 일별 집계 단위라 시계열 변동성이 단조로울 수 있어, 통계모델 대비 딥러닝 우위를 명확히 보이는 비교실험 설계가 중요. 장애유형별 세분화 데이터는 비공개라 형평성 분석은 지역 단위(저상버스 보급률 등)로 제한됨</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>AI허브 데이터의 턱낮춤/점자블록 라벨 단위가 서비스에 필요한 수준(개별 지점 좌표)인지 사전 확인 필요. 기존 서울동행맵과 차별화 포인트(자동 갱신 vs 수동 입력)를 명확히 해야 함</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>정형데이터 특성상 '왜 딥러닝인가' 방어가 필요(이동약자_이동성_프로젝트_개요.md에서 이미 지적된 문제). PSI 원자료 접근 경로 추가 확인 필요</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>평가용 Q&amp;A 셋을 직접 소량 제작해야 함(5순위와 동일한 리스크)</t>
         </is>
       </c>
     </row>

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -53,17 +53,6 @@
       <family val="3"/>
       <sz val="8"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -154,7 +143,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,13 +514,13 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="9"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14.75" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="8"/>
+    <col width="19.875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="43.375" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="34" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="27.625" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="20.75" bestFit="1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -844,7 +833,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>TFT, PatchTST, N-BEATS, XGBoost/LightGBM 비교, SHAP (1순위 기법을 콜택시 수요예측에 적용)</t>
+          <t>TFT, PatchTST, N-BEATS, XGBoost/LightGBM 비교, SHAP (1순위 기법을 콜택시 수요예측에 적용) + 저상버스 보급률을 정적 외생변수/SHAP 피처로 결합해 형평성 정량 분석</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -863,7 +852,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="339.95" customHeight="1">
+    <row r="6" ht="380" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>데이터셋 여부</t>
@@ -953,7 +942,10 @@
 - 장애인콜택시 일별 이용현황: https://data.seoul.go.kr/dataList/OA-13550/L/1/datasetView.do
 - 장애인콜택시 탑승내역(개별 이력): https://www.data.go.kr/data/15115859/fileData.do
 - 장애인콜시스템정보: https://data.seoul.go.kr/dataList/OA-15558/A/1/datasetView.do
-- 기상자료개방포털: https://data.kma.go.kr/</t>
+- 기상자료개방포털: https://data.kma.go.kr/
+[형평성 분석용 보조 데이터 - 저상버스 보급률]
+- 한국교통안전공단_지역별 저상버스 보급현황(전국, 17개 광역지자체, 2021 스냅샷): https://www.data.go.kr/data/15106061/fileData.do
+- 서울특별시_저상버스 도입 노선 및 노선별 보유율(노선 단위, CSV): https://www.data.go.kr/data/15086332/fileData.do?recommendDataYn=Y</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -1182,7 +1174,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="200" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>비고/리스크</t>
@@ -1230,7 +1222,8 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>콜택시 데이터가 일별 집계 단위라 시계열 변동성이 단조로울 수 있어, 통계모델 대비 딥러닝 우위를 명확히 보이는 비교실험 설계가 중요. 장애유형별 세분화 데이터는 비공개라 형평성 분석은 지역 단위(저상버스 보급률 등)로 제한됨</t>
+          <t>콜택시 데이터가 일별 집계 단위라 시계열 변동성이 단조로울 수 있어, 통계모델 대비 딥러닝 우위를 명확히 보이는 비교실험 설계가 중요. 장애유형별 세분화 데이터는 비공개라 형평성 분석은 지역 단위(저상버스 보급률 등)로 제한됨
+저상버스 보급률은 시계열이 아닌 스냅샷(전국 2021년 기준 17행)이라 단독 학습에는 부적합 - 콜택시 수요예측 모델의 정적 외생변수 또는 2차 SHAP 해석모델의 피처로 활용. 전국 데이터(광역 단위)와 서울 노선 데이터(노선 단위)는 granularity가 달라 자치구 단위로 집계 정합 필요.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="종합비교표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종합비교표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'종합비교표'!$A$1:$I$10</definedName>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.75" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,7 @@
     <col width="34" bestFit="1" customWidth="1" min="11" max="11"/>
     <col width="27.625" bestFit="1" customWidth="1" min="12" max="12"/>
     <col width="20.75" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -589,6 +590,11 @@
           <t>12 (이동약자 정책 RAG)</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13 (10+11 결합: 보행약자 통합)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -640,6 +646,11 @@
           <t>12 (이동약자 정책 RAG)</t>
         </is>
       </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>13 (10+11 결합: 보행약자 통합)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -717,6 +728,12 @@
           <t>이동약자 정책·복지 제도 Q&amp;A RAG 서비스</t>
         </is>
       </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>보행약자(장애인+고령자) 안전·접근성 통합 서비스
+(10번 CV 접근성 매핑 + 11번 고령 보행자 사고위험 결합)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="54.95" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -784,8 +801,13 @@
           <t>NLP / RAG</t>
         </is>
       </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Computer Vision / 공간AI + Tabular (멀티모듈)</t>
+        </is>
+      </c>
     </row>
-    <row r="5" ht="95.09999999999999" customHeight="1">
+    <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>핵심 모델/기술</t>
@@ -849,6 +871,13 @@
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>LangChain/LlamaIndex, BGE-m3 임베딩, Hybrid Search(FAISS/Qdrant), 한국어 sLLM, RAGAS</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>[모듈1-접근성] YOLOv8/v11 또는 SAM 세그멘테이션으로 턱낮춤·점자블록·경사로 탐지 → 접근성 점수화
+[모듈2-사고위험] XGBoost/TabNet 기반 지역별 고령 보행자 사고위험지수 예측(자체 설계, 선행연구 PSI 방법론 참고) + SHAP 해석
+[결합] Folium/Streamlit 지도에 '접근성 낮음 + 사고위험 높음' 지역을 오버레이해 우선순위 시각화</t>
         </is>
       </c>
     </row>
@@ -972,6 +1001,17 @@
 - 복지로: https://www.bokjiro.go.kr/</t>
         </is>
       </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>있음(부분) - CV는 AI허브 보행 안전 도로시설물 데이터(102.5만 장, 승인 필요), 사고위험·복지 데이터는 공공데이터포털/서울 열린데이터광장에서 즉시 다운로드 가능
+[데이터셋 링크]
+- AI허브 보행 안전을 위한 도로 시설물 데이터: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
+- 도로교통공단_시군구별 월별 교통사고 통계: https://www.data.go.kr/data/15070295/fileData.do
+- 서울시 교통사고 현황(연령층별 사상자): https://data.seoul.go.kr/dataList/10754/S/2/datasetView.do
+- 서울시 보행 교통사고 현황: https://data.seoul.go.kr/dataList/324/S/2/datasetView.do
+- 보건복지부_노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1039,6 +1079,11 @@
           <t>즉시 수집 가능 (라벨링 불필요, 문서 수집형 과제)</t>
         </is>
       </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>혼재 - 사고통계·복지시설 데이터는 즉시 다운로드 가능, CV용 AI허브 데이터는 승인 필요(대기 리스크)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1106,6 +1151,11 @@
           <t>상</t>
         </is>
       </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>중 - 두 모듈 통합 범위 조정 필요(자치구 1곳 파일럿 권장)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1173,6 +1223,11 @@
           <t>Hybrid Search·Re-ranking·환각 방지 정량평가로 RAG 트렌드 적합성 입증, '내가 받을 수 있는 지원제도 찾기'라는 실사용 시나리오가 명확</t>
         </is>
       </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>장애인·고령자를 아우르는 '보행약자' 전체를 대상으로 한 통합 안전·접근성 지도 서비스. CV(객체탐지)와 정형데이터 해석(SHAP)을 하나의 서비스로 엮는 멀티모듈 설계 역량, PSI 지표를 선행연구 방법론 참고해 자체 설계한 문제해결 서사</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="200" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1239,6 +1294,11 @@
       <c r="M10" s="4" t="inlineStr">
         <is>
           <t>평가용 Q&amp;A 셋을 직접 소량 제작해야 함(5순위와 동일한 리스크)</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>AI허브 승인 지연 시 Roboflow/Kaggle 대체 데이터로 CV 모듈만 축소 진행 가능. 4인이 CV팀/정형데이터팀으로 병렬 진행해도 결합 단계(지도 오버레이)에서 시간 압박 가능 - 1개 자치구로 범위를 좁히는 것을 권장. PSI 원자료는 비공개라 사고건수+연령대+노인복지시설 밀도로 자체 위험지수 설계.</t>
         </is>
       </c>
     </row>

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종합비교표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="종합비교표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'종합비교표'!$A$1:$I$10</definedName>
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.75" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -522,6 +522,7 @@
     <col width="27.625" bestFit="1" customWidth="1" min="12" max="12"/>
     <col width="20.75" bestFit="1" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -595,6 +596,11 @@
           <t>13 (10+11 결합: 보행약자 통합)</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14 (9+13 결합)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -651,6 +657,11 @@
           <t>13 (10+11 결합: 보행약자 통합)</t>
         </is>
       </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>14 (9+13 결합)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -734,6 +745,12 @@
 (10번 CV 접근성 매핑 + 11번 고령 보행자 사고위험 결합)</t>
         </is>
       </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>이동약자 이동성+보행안전 통합 대시보드
+(9번 콜택시 수요예측·형평성 분석 + 13번 보행약자 접근성·사고위험 결합, 느슨결합)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="54.95" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -806,6 +823,11 @@
           <t>Computer Vision / 공간AI + Tabular (멀티모듈)</t>
         </is>
       </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Time-Series + Computer Vision + Tabular (느슨결합 멀티모듈)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="130" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -878,6 +900,14 @@
           <t>[모듈1-접근성] YOLOv8/v11 또는 SAM 세그멘테이션으로 턱낮춤·점자블록·경사로 탐지 → 접근성 점수화
 [모듈2-사고위험] XGBoost/TabNet 기반 지역별 고령 보행자 사고위험지수 예측(자체 설계, 선행연구 PSI 방법론 참고) + SHAP 해석
 [결합] Folium/Streamlit 지도에 '접근성 낮음 + 사고위험 높음' 지역을 오버레이해 우선순위 시각화</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>[모듈A-수요예측, 9번 재사용] TFT/PatchTST/N-BEATS + XGBoost/LightGBM 비교, SHAP (저상버스 보급률을 정적 외생변수로 결합)
+[모듈B-접근성, 13번 모듈1 재사용] YOLOv8/v11·SAM 세그멘테이션 → 턱낮춤·점자블록 탐지 → 접근성 점수화
+[모듈C-사고위험, 13번 모듈2 재사용] XGBoost/TabNet 기반 사고위험지수 예측 + SHAP 해석
+[결합] 3개 모델을 하나로 합치지 않고 각각 독립 완성 후, Streamlit/Folium 대시보드에서 자치구 단위로 수요 히트맵 + 접근성 점수 + 사고위험 점수를 레이어로 오버레이</t>
         </is>
       </c>
     </row>
@@ -1012,6 +1042,19 @@
 - 보건복지부_노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
         </is>
       </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>있음 - 9번(J열)·13번(N열) 데이터셋을 그대로 재사용, 신규 데이터 수집 없음
+[데이터셋 링크] J6·N6과 동일
+- 장애인콜택시 일별 이용현황: https://data.seoul.go.kr/dataList/OA-13550/L/1/datasetView.do
+- 장애인콜택시 탑승내역: https://www.data.go.kr/data/15115859/fileData.do
+- 저상버스 보급현황(전국): https://www.data.go.kr/data/15106061/fileData.do
+- 서울 저상버스 노선별 보유율: https://www.data.go.kr/data/15086332/fileData.do?recommendDataYn=Y
+- AI허브 보행 안전을 위한 도로 시설물 데이터: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
+- 도로교통공단_시군구별 월별 교통사고 통계: https://www.data.go.kr/data/15070295/fileData.do
+- 보건복지부_노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1084,6 +1127,11 @@
           <t>혼재 - 사고통계·복지시설 데이터는 즉시 다운로드 가능, CV용 AI허브 데이터는 승인 필요(대기 리스크)</t>
         </is>
       </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>혼재 - 콜택시·형평성·사고통계·복지시설 데이터는 즉시 다운로드(9번과 동일), CV용 AI허브 보행시설물 데이터만 승인 필요(13번과 동일 리스크 유지)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1156,6 +1204,11 @@
           <t>중 - 두 모듈 통합 범위 조정 필요(자치구 1곳 파일럿 권장)</t>
         </is>
       </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>중 - 모듈별로는 9번(상)·13번(중) 파이프라인을 그대로 재사용해 신규 개발 부담은 적으나, 마지막 대시보드 결합 단계에서 시간 압박 가능. 4인을 수요예측팀/CV팀/정형데이터팀/통합·대시보드팀으로 병렬 배치 권장</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1228,6 +1281,11 @@
           <t>장애인·고령자를 아우르는 '보행약자' 전체를 대상으로 한 통합 안전·접근성 지도 서비스. CV(객체탐지)와 정형데이터 해석(SHAP)을 하나의 서비스로 엮는 멀티모듈 설계 역량, PSI 지표를 선행연구 방법론 참고해 자체 설계한 문제해결 서사</t>
         </is>
       </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>이동약자의 '이동(콜택시)'과 '보행(접근성·사고위험)' 두 축을 모두 아우르는 종합 서비스 서사. 시계열·CV·정형데이터 3가지 모델링 기법을 한 프로젝트에서 시연해 기술 폭을 어필하고, 형평성(저상버스)부터 인프라 우선순위(사고위험)까지 정책 제언 스펙트럼을 확장</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="200" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1299,6 +1357,11 @@
       <c r="N10" s="4" t="inlineStr">
         <is>
           <t>AI허브 승인 지연 시 Roboflow/Kaggle 대체 데이터로 CV 모듈만 축소 진행 가능. 4인이 CV팀/정형데이터팀으로 병렬 진행해도 결합 단계(지도 오버레이)에서 시간 압박 가능 - 1개 자치구로 범위를 좁히는 것을 권장. PSI 원자료는 비공개라 사고건수+연령대+노인복지시설 밀도로 자체 위험지수 설계.</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>핵심은 모델을 억지로 하나로 합치지 않고 9번·13번을 독립 모듈로 유지한 채 시각화 레이어에서만 결합하는 것 - 이렇게 하면 9번의 '상' 실현성과 13번의 '중' 실현성을 각각 훼손하지 않음. 시간이 부족하면 9번(콜택시)만 완성하고 13번은 축소해도 발표 서사 손실이 적음(모듈 분리형 설계라 부분 완성도 가능). CV 모듈 승인 지연 시 13번과 동일하게 Roboflow/Kaggle 대체 데이터로 축소</t>
         </is>
       </c>
     </row>

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -60,8 +60,18 @@
       <family val="3"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +102,68 @@
         <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009DD9C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD9C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -116,11 +186,179 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0000695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="medium">
+        <color rgb="0000695C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0000695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0000695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0000695C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="0000695C"/>
+      </right>
+      <top style="medium">
+        <color rgb="0000695C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="0000695C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="0000695C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0000695C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00695C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF00695C"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00695C"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00695C"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF00695C"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00695C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF00695C"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF00695C"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +384,176 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -511,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.75" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -531,72 +939,72 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>1순위</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>2순위</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>3순위</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>4순위</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="43" t="inlineStr">
         <is>
           <t>5순위</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="43" t="inlineStr">
         <is>
           <t>6순위</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="44" t="inlineStr">
         <is>
           <t>7순위</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="43" t="inlineStr">
         <is>
           <t>8순위</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="44" t="inlineStr">
         <is>
           <t>9 (1+7 결합)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="45" t="inlineStr">
         <is>
           <t>10 (CV: 보행 접근성 매핑)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="46" t="inlineStr">
         <is>
           <t>11 (고령 보행자 사고위험 예측)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="47" t="inlineStr">
         <is>
           <t>12 (이동약자 정책 RAG)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="48" t="inlineStr">
         <is>
           <t>13 (10+11 결합: 보행약자 통합)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="49" t="inlineStr">
         <is>
           <t>14 (9+13 결합)</t>
         </is>
@@ -608,56 +1016,56 @@
           <t>순위</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="51" t="inlineStr">
         <is>
           <t>9 (1+7 결합)</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="52" t="inlineStr">
         <is>
           <t>10 (CV: 보행 접근성 매핑)</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="53" t="inlineStr">
         <is>
           <t>11 (고령 보행자 사고위험 예측)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="54" t="inlineStr">
         <is>
           <t>12 (이동약자 정책 RAG)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="55" t="inlineStr">
         <is>
           <t>13 (10+11 결합: 보행약자 통합)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="56" t="inlineStr">
         <is>
           <t>14 (9+13 결합)</t>
         </is>
@@ -669,83 +1077,82 @@
           <t>주제</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>복합변수 기반 도심 수요/유동인구
-시계열 예측</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
+        <is>
+          <t>도시 에너지 인프라 수요관리</t>
+        </is>
+      </c>
+      <c r="C3" s="57" t="inlineStr">
         <is>
           <t>데이터 불균형 환경에서의
 이상징후 감지</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>독거노인 위급상황 자동 탐지
 (낙상 감지)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="57" t="inlineStr">
         <is>
           <t>도심 시설물 및 위험요소
 자동 탐지</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="57" t="inlineStr">
         <is>
           <t>공공/정책 문서 기반
 멀티모달 RAG 서비스 에이전트</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="57" t="inlineStr">
         <is>
           <t>에어컨 실외기 열화상 기반
 이상 탐지</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="58" t="inlineStr">
         <is>
           <t>이동약자 대중교통
 이동성 분석</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="57" t="inlineStr">
         <is>
           <t>고랭지 농작물 폭염·열 스트레스
 예방/예찰 시스템</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="58" t="inlineStr">
         <is>
           <t>장애인콜택시(특별교통수단) 수요 예측 및 지역 형평성 분석
 (1순위 + 7순위 결합)</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="59" t="inlineStr">
         <is>
           <t>보행로 접근성 시설물 자동 탐지 및 매핑 서비스
 (이동약자 데이터에서 파생, CV)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="60" t="inlineStr">
         <is>
           <t>고령 보행자 교통사고 위험 예측 및 인프라 우선순위 분석</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="61" t="inlineStr">
         <is>
           <t>이동약자 정책·복지 제도 Q&amp;A RAG 서비스</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="62" t="inlineStr">
         <is>
           <t>보행약자(장애인+고령자) 안전·접근성 통합 서비스
 (10번 CV 접근성 매핑 + 11번 고령 보행자 사고위험 결합)</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="63" t="inlineStr">
         <is>
           <t>이동약자 이동성+보행안전 통합 대시보드
 (9번 콜택시 수요예측·형평성 분석 + 13번 보행약자 접근성·사고위험 결합, 느슨결합)</t>
@@ -758,72 +1165,72 @@
           <t>분야</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>Time-Series</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="57" t="inlineStr">
         <is>
           <t>Anomaly Detection</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="57" t="inlineStr">
         <is>
           <t>Computer Vision</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="57" t="inlineStr">
         <is>
           <t>Computer Vision / 공간AI</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="57" t="inlineStr">
         <is>
           <t>NLP / Multimodal / RAG</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="57" t="inlineStr">
         <is>
           <t>Computer Vision (열화상)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="58" t="inlineStr">
         <is>
           <t>정책분석 → CV(포트홀)/NLP(리뷰 감성분석)로 축소 권고</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="57" t="inlineStr">
         <is>
           <t>Time-Series + CV + 강화학습 (멀티모듈)</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="58" t="inlineStr">
         <is>
           <t>Time-Series + 정책분석(형평성)</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="59" t="inlineStr">
         <is>
           <t>Computer Vision / 공간AI</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="60" t="inlineStr">
         <is>
           <t>Time-Series/Tabular + 공간분석</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="61" t="inlineStr">
         <is>
           <t>NLP / RAG</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="62" t="inlineStr">
         <is>
           <t>Computer Vision / 공간AI + Tabular (멀티모듈)</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="63" t="inlineStr">
         <is>
           <t>Time-Series + Computer Vision + Tabular (느슨결합 멀티모듈)</t>
         </is>
@@ -835,74 +1242,74 @@
           <t>핵심 모델/기술</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>TFT, PatchTST, N-BEATS, XGBoost/LightGBM 비교, SHAP</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="57" t="inlineStr">
         <is>
           <t>Autoencoder, Isolation Forest, AnomalyCLIP, Focal Loss</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>YOLO 객체탐지 + 포즈추정/바운딩박스 종횡비 변화 + CNN 분류</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>YOLOv8/v11, SAM, ONNX/TensorRT, Folium·Streamlit</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="57" t="inlineStr">
         <is>
           <t>LangChain/LlamaIndex, BGE-m3, FAISS/Qdrant Hybrid Search, 한국어 sLLM, RAGAS</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="57" t="inlineStr">
         <is>
           <t>전이학습 CNN(ResNet/EfficientNet), YOLO(이상부위 위치 탐지)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="58" t="inlineStr">
         <is>
           <t>(포트홀 축소 시) YOLO/CNN, (리뷰 축소 시) 감성분류 모델</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>LSTM/Informer(모듈1), YOLOv8/ViT 열화상-RGB Fusion(모듈2), DQN/PPO(모듈3)</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="58" t="inlineStr">
         <is>
           <t>TFT, PatchTST, N-BEATS, XGBoost/LightGBM 비교, SHAP (1순위 기법을 콜택시 수요예측에 적용) + 저상버스 보급률을 정적 외생변수/SHAP 피처로 결합해 형평성 정량 분석</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="59" t="inlineStr">
         <is>
           <t>YOLOv8/v11 객체탐지 또는 SAM 세그멘테이션(턱낮춤·점자블록·계단/장애물 탐지), 좌표 매핑 후 접근성 점수화, Folium/Streamlit 지도</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="60" t="inlineStr">
         <is>
           <t>TabNet 또는 지역 그래프 기반 GNN, XGBoost 베이스라인 비교, SHAP 해석</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="61" t="inlineStr">
         <is>
           <t>LangChain/LlamaIndex, BGE-m3 임베딩, Hybrid Search(FAISS/Qdrant), 한국어 sLLM, RAGAS</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="62" t="inlineStr">
         <is>
           <t>[모듈1-접근성] YOLOv8/v11 또는 SAM 세그멘테이션으로 턱낮춤·점자블록·경사로 탐지 → 접근성 점수화
 [모듈2-사고위험] XGBoost/TabNet 기반 지역별 고령 보행자 사고위험지수 예측(자체 설계, 선행연구 PSI 방법론 참고) + SHAP 해석
 [결합] Folium/Streamlit 지도에 '접근성 낮음 + 사고위험 높음' 지역을 오버레이해 우선순위 시각화</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>[모듈A-수요예측, 9번 재사용] TFT/PatchTST/N-BEATS + XGBoost/LightGBM 비교, SHAP (저상버스 보급률을 정적 외생변수로 결합)
 [모듈B-접근성, 13번 모듈1 재사용] YOLOv8/v11·SAM 세그멘테이션 → 턱낮춤·점자블록 탐지 → 접근성 점수화
@@ -917,7 +1324,7 @@
           <t>데이터셋 여부</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>있음 - 서울 열린데이터광장(따릉이, 지하철/버스 승하차), 기상청 기상자료개방포털, 공공데이터포털 전력소비량
 [데이터셋 링크]
@@ -928,7 +1335,7 @@
 - 전력사용량(지역별·용도별): https://www.data.go.kr/data/15031941/fileData.do</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>있음 - MVTec AD(표준 벤치마크), Kaggle 안전모 착용탐지, AI허브 산업단지 열화상(약 103만 장)
 [데이터셋 링크]
@@ -937,7 +1344,7 @@
 - AI허브 열화상카메라이미지(산업단지): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=235</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>있음 - URFD·Le2i(해외, 즉시), AI허브 낙상사고 위험동작 영상-센서쌍(승인 필요)
 [데이터셋 링크]
@@ -946,7 +1353,7 @@
 - AI허브 낙상사고 위험동작 영상-센서: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=71641</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="57" t="inlineStr">
         <is>
           <t>있음 - AI허브 도로 노면결함·포트홀 이미지(승인 필요), Kaggle pothole detection(즉시)
 [데이터셋 링크]
@@ -955,7 +1362,7 @@
 - Kaggle Pothole Detection(즉시): https://www.kaggle.com/datasets/andrewmvd/pothole-detection</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="57" t="inlineStr">
         <is>
           <t>있음(문서 수집형) - 공공데이터포털, 국가법령정보센터, 복지로 등 정책 문서
 [데이터셋 링크]
@@ -964,7 +1371,7 @@
 - 복지로: https://www.bokjiro.go.kr/</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="64" t="inlineStr">
         <is>
           <t>실외기 전용 데이터 없음 - AI허브 산업단지 열화상(승인 필요), Kaggle 태양광 열화상(즉시)으로 대체
 [데이터셋 링크] (실외기 전용은 없음 → 대체/포함 데이터로 보완)
@@ -973,7 +1380,7 @@
 - Kaggle Photovoltaic System Thermography: https://www.kaggle.com/datasets/marcosgabriel/photovoltaic-system-thermography</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="58" t="inlineStr">
         <is>
           <t>이동 이벤트 데이터는 공개(장애인콜택시 탑승내역 등, 서울시설공단/공공데이터포털). 단 장애유형·정도 결합 데이터는 비공개
 [데이터셋 링크]
@@ -983,7 +1390,7 @@
 - 교통약자이동지원센터표준데이터: https://www.data.go.kr/data/15028207/standard.do</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>부분적 - 모듈2(작물 병해 이미지)는 AI허브 '노지 작물 질병/해충 진단 이미지'(35만~50만 건, 승인 필요), DACON 대안 존재. 모듈1은 위험지수 라벨 직접 설계 필요. 모듈3은 데이터 없음
 [데이터셋 링크]
@@ -994,7 +1401,7 @@
 - (모듈3, 데이터 없음 → 대체) Autonomous Greenhouse Challenge(관수/기후제어 시계열): https://data.4tu.nl/articles/_/12764777/2</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="58" t="inlineStr">
         <is>
           <t>있음 - 장애인콜택시 일별 이용현황(서울시설공단/공공데이터포털), 장애인콜시스템정보(서울 열린데이터광장), 기상청 기상자료개방포털(외생변수로 결합)
 [데이터셋 링크]
@@ -1007,7 +1414,7 @@
 - 서울특별시_저상버스 도입 노선 및 노선별 보유율(노선 단위, CSV): https://www.data.go.kr/data/15086332/fileData.do?recommendDataYn=Y</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="59" t="inlineStr">
         <is>
           <t>있음(부분) - AI허브 '보행 안전을 위한 도로 시설물 데이터'(약 102.5만 장, 안전·관리·환경·편의시설 유형별 양호/불량 판정, 턱낮춤·점자블록 포함, 승인 필요)
 [데이터셋 링크]
@@ -1015,7 +1422,7 @@
 - AI허브 1인칭 시점 보행영상(보조자료): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=159</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="60" t="inlineStr">
         <is>
           <t>부분적 - TAAS(도로교통공단 교통사고분석시스템)에서 지역별·연령별 사고통계 조회 가능(대량 다운로드는 번거로움), 노인복지시설 위치는 공공데이터포털에서 확보 가능. PSI 지표 원자료 공개 여부는 미확인 → 직접 위험지수를 설계해야 할 가능성이 높음
 [데이터셋 링크]
@@ -1023,7 +1430,7 @@
 - 보건복지부 노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="61" t="inlineStr">
         <is>
           <t>있음(문서 수집형) - 국가법령정보 공동활용 API(교통약자의 이동편의 증진법 등), 복지로, '이동약자_대중교통_국내외비교_보고서.docx' 자체도 코퍼스로 활용 가능
 [데이터셋 링크]
@@ -1031,7 +1438,7 @@
 - 복지로: https://www.bokjiro.go.kr/</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="62" t="inlineStr">
         <is>
           <t>있음(부분) - CV는 AI허브 보행 안전 도로시설물 데이터(102.5만 장, 승인 필요), 사고위험·복지 데이터는 공공데이터포털/서울 열린데이터광장에서 즉시 다운로드 가능
 [데이터셋 링크]
@@ -1042,7 +1449,7 @@
 - 보건복지부_노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="63" t="inlineStr">
         <is>
           <t>있음 - 9번(J열)·13번(N열) 데이터셋을 그대로 재사용, 신규 데이터 수집 없음
 [데이터셋 링크] J6·N6과 동일
@@ -1062,72 +1469,72 @@
           <t>데이터 확보 난이도</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>즉시 다운로드 (승인 절차 없음)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="57" t="inlineStr">
         <is>
           <t>MVTec은 즉시, AI허브는 승인 필요</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>URFD는 규모가 작아 즉시 학습·검증 가능</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="57" t="inlineStr">
         <is>
           <t>혼재 (일부 즉시, 일부 승인 필요)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="57" t="inlineStr">
         <is>
           <t>즉시 수집 가능 (라벨링 데이터셋이 아닌 문서 수집 과제)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="57" t="inlineStr">
         <is>
           <t>대체 데이터 기준 중</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="58" t="inlineStr">
         <is>
           <t>이동 이벤트 데이터는 즉시, 유형 결합 데이터는 MDIS 등 별도 승인 필요해 사실상 불가</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="57" t="inlineStr">
         <is>
           <t>모듈별 상이 (모듈2만 승인 시 확보 가능)</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="58" t="inlineStr">
         <is>
           <t>즉시 다운로드 (승인 절차 없음, 1순위·7순위 데이터 그대로 재사용)</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="59" t="inlineStr">
         <is>
           <t>AI허브 승인 필요 - 대기시간이 2일 일정에 리스크. 승인 지연 시 Roboflow/Kaggle의 sidewalk·curb-ramp 데이터로 즉시 대체 검증 필요(별도 확인 필요)</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="60" t="inlineStr">
         <is>
           <t>혼재 - TAAS는 웹 통계 조회 중심이라 벌크 다운로드가 번거로움. PSI 원자료 미확인은 추가 리스크</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="61" t="inlineStr">
         <is>
           <t>즉시 수집 가능 (라벨링 불필요, 문서 수집형 과제)</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="62" t="inlineStr">
         <is>
           <t>혼재 - 사고통계·복지시설 데이터는 즉시 다운로드 가능, CV용 AI허브 데이터는 승인 필요(대기 리스크)</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="63" t="inlineStr">
         <is>
           <t>혼재 - 콜택시·형평성·사고통계·복지시설 데이터는 즉시 다운로드(9번과 동일), CV용 AI허브 보행시설물 데이터만 승인 필요(13번과 동일 리스크 유지)</t>
         </is>
@@ -1199,12 +1606,12 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="N8" s="65" t="inlineStr">
         <is>
           <t>중 - 두 모듈 통합 범위 조정 필요(자치구 1곳 파일럿 권장)</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="66" t="inlineStr">
         <is>
           <t>중 - 모듈별로는 9번(상)·13번(중) 파이프라인을 그대로 재사용해 신규 개발 부담은 적으나, 마지막 대시보드 결합 단계에서 시간 압박 가능. 4인을 수요예측팀/CV팀/정형데이터팀/통합·대시보드팀으로 병렬 배치 권장</t>
         </is>
@@ -1216,72 +1623,72 @@
           <t>채용 어필 포인트</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="57" t="inlineStr">
         <is>
           <t>통계/ML 모델 대비 딥러닝 성능 비교(RMSE·MAE) + XAI 해석 + 정책 제언까지 연결</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="57" t="inlineStr">
         <is>
           <t>실무 데이터 특성(정상 다수/이상 극소수)을 다뤄본 경험, F1·PR Curve 등 불균형 특화 평가지표 활용</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>골든타임 확보라는 강한 사회적 스토리 + 사전학습 모델 활용으로 구현 난이도 낮음</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="57" t="inlineStr">
         <is>
           <t>mAP 개선뿐 아니라 실시간 추론속도(FPS) 최적화 + GIS 핫스팟 대시보드로 실무형 결과물 제시</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="57" t="inlineStr">
         <is>
           <t>Hybrid Search·Re-ranking·환각 방지 정량평가로 LLM/RAG 트렌드 적합성 입증</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="57" t="inlineStr">
         <is>
           <t>화재예방이라는 실생활 문제 + '데이터 부재를 동일 구조 데이터로 검증했다'는 문제해결 서사</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="58" t="inlineStr">
         <is>
           <t>인구 30.9%에 해당하는 사회문제 + 국내외 정량 격차 비교 서사</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="57" t="inlineStr">
         <is>
           <t>기후플레이션과 연결되는 강한 사회적 서사, 단 전체 시스템은 2일 범위를 초과</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="58" t="inlineStr">
         <is>
           <t>통계/ML 대비 딥러닝 시계열 성능 비교(RMSE·MAE) + XAI 해석에 이동약자 수요예측이라는 사회적 임팩트까지 결합 - 기술력과 서사를 동시에 어필</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K9" s="59" t="inlineStr">
         <is>
           <t>단순 mAP 개선이 아니라 '접근성 점수화' 로직 설계 + GIS 대시보드로 실무형 결과물. 보고서에서 확인된 '전용 앱 정보가 부정확하다'는 실제 문제(머니투데이 2024.10.15)를 기술로 보완하는 서사</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="60" t="inlineStr">
         <is>
           <t>정형 데이터에서 딥러닝이 통계모델보다 실제로 나은지 비교검증 + 위험 인프라 우선순위 정책 제언까지 연결</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" s="61" t="inlineStr">
         <is>
           <t>Hybrid Search·Re-ranking·환각 방지 정량평가로 RAG 트렌드 적합성 입증, '내가 받을 수 있는 지원제도 찾기'라는 실사용 시나리오가 명확</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="62" t="inlineStr">
         <is>
           <t>장애인·고령자를 아우르는 '보행약자' 전체를 대상으로 한 통합 안전·접근성 지도 서비스. CV(객체탐지)와 정형데이터 해석(SHAP)을 하나의 서비스로 엮는 멀티모듈 설계 역량, PSI 지표를 선행연구 방법론 참고해 자체 설계한 문제해결 서사</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="O9" s="63" t="inlineStr">
         <is>
           <t>이동약자의 '이동(콜택시)'과 '보행(접근성·사고위험)' 두 축을 모두 아우르는 종합 서비스 서사. 시계열·CV·정형데이터 3가지 모델링 기법을 한 프로젝트에서 시연해 기술 폭을 어필하고, 형평성(저상버스)부터 인프라 우선순위(사고위험)까지 정책 제언 스펙트럼을 확장</t>
         </is>
@@ -1293,75 +1700,130 @@
           <t>비고/리스크</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="57" t="inlineStr">
         <is>
           <t>6개 후보 중 착수 장벽이 가장 낮음</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>가장 '실무 티'가 나는 주제로 평가</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>Le2i는 원본 사이트 접속 불가, 미러 확보 필요</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="57" t="inlineStr">
         <is>
           <t>세부 주제(쓰레기 무단투기 등)는 데이터 개별 확인 필요</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="57" t="inlineStr">
         <is>
           <t>평가용 Q&amp;A 셋을 직접 소량 제작해야 함</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>실외기 직접 촬영은 장비·시간상 2일 내 비현실적</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="58" t="inlineStr">
         <is>
           <t>정형데이터에 딥러닝을 억지로 적용하면 오버엔지니어링 감점 위험. 정책분석 보고서(docx)는 별도 존재</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="57" t="inlineStr">
         <is>
           <t>보유 중인 기상청 폭염데이터(2019~2026, 약 200개 지점 일별)로 모듈1 보조 가능</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="58" t="inlineStr">
         <is>
           <t>콜택시 데이터가 일별 집계 단위라 시계열 변동성이 단조로울 수 있어, 통계모델 대비 딥러닝 우위를 명확히 보이는 비교실험 설계가 중요. 장애유형별 세분화 데이터는 비공개라 형평성 분석은 지역 단위(저상버스 보급률 등)로 제한됨
 저상버스 보급률은 시계열이 아닌 스냅샷(전국 2021년 기준 17행)이라 단독 학습에는 부적합 - 콜택시 수요예측 모델의 정적 외생변수 또는 2차 SHAP 해석모델의 피처로 활용. 전국 데이터(광역 단위)와 서울 노선 데이터(노선 단위)는 granularity가 달라 자치구 단위로 집계 정합 필요.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="59" t="inlineStr">
         <is>
           <t>AI허브 데이터의 턱낮춤/점자블록 라벨 단위가 서비스에 필요한 수준(개별 지점 좌표)인지 사전 확인 필요. 기존 서울동행맵과 차별화 포인트(자동 갱신 vs 수동 입력)를 명확히 해야 함</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="60" t="inlineStr">
         <is>
           <t>정형데이터 특성상 '왜 딥러닝인가' 방어가 필요(이동약자_이동성_프로젝트_개요.md에서 이미 지적된 문제). PSI 원자료 접근 경로 추가 확인 필요</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="61" t="inlineStr">
         <is>
           <t>평가용 Q&amp;A 셋을 직접 소량 제작해야 함(5순위와 동일한 리스크)</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="67" t="inlineStr">
         <is>
           <t>AI허브 승인 지연 시 Roboflow/Kaggle 대체 데이터로 CV 모듈만 축소 진행 가능. 4인이 CV팀/정형데이터팀으로 병렬 진행해도 결합 단계(지도 오버레이)에서 시간 압박 가능 - 1개 자치구로 범위를 좁히는 것을 권장. PSI 원자료는 비공개라 사고건수+연령대+노인복지시설 밀도로 자체 위험지수 설계.</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="O10" s="68" t="inlineStr">
         <is>
           <t>핵심은 모델을 억지로 하나로 합치지 않고 9번·13번을 독립 모듈로 유지한 채 시각화 레이어에서만 결합하는 것 - 이렇게 하면 9번의 '상' 실현성과 13번의 '중' 실현성을 각각 훼손하지 않음. 시간이 부족하면 9번(콜택시)만 완성하고 13번은 축소해도 발표 서사 손실이 적음(모듈 분리형 설계라 부분 완성도 가능). CV 모듈 승인 지연 시 13번과 동일하게 Roboflow/Kaggle 대체 데이터로 축소</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>범례 (주제 유사 그룹)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="69" t="inlineStr"/>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>독립 원안 (1,2,3,4,5,6,8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="70" t="inlineStr"/>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>이동약자 - 시계열 (7, 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="71" t="inlineStr"/>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>이동약자 - CV 접근성 (10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="72" t="inlineStr"/>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>이동약자 - 사고위험 (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="73" t="inlineStr"/>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>이동약자 - RAG (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="74" t="inlineStr"/>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>이동약자 - 결합 (13, 14)</t>
         </is>
       </c>
     </row>

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -1127,7 +1127,7 @@
       <c r="J3" s="58" t="inlineStr">
         <is>
           <t>장애인콜택시(특별교통수단) 수요 예측 및 지역 형평성 분석
-(1순위 + 7순위 결합)</t>
+(1순위 기법 + 7순위 주제 결합)</t>
         </is>
       </c>
       <c r="K3" s="59" t="inlineStr">

--- a/딥러닝_프로젝트_종합비교표.xlsx
+++ b/딥러닝_프로젝트_종합비교표.xlsx
@@ -1419,14 +1419,19 @@
           <t>있음(부분) - AI허브 '보행 안전을 위한 도로 시설물 데이터'(약 102.5만 장, 안전·관리·환경·편의시설 유형별 양호/불량 판정, 턱낮춤·점자블록 포함, 승인 필요)
 [데이터셋 링크]
 - AI허브 보행 안전을 위한 도로 시설물 데이터: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
-- AI허브 1인칭 시점 보행영상(보조자료): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=159</t>
+- AI허브 1인칭 시점 보행영상(보조자료): https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=159
+[승인 지연 시 즉시 대체 - 검증 완료]
+- Roboflow Universe "accessibility street"(ramps-curbs 4,968장, 프리트레인 모델 포함): https://universe.roboflow.com/tfg-7qtpm/accesibility-street
+- Kaggle "Sidewalk Segment Dataset"(VOC2007 포맷): https://www.kaggle.com/datasets/lemnix/sidewalk-segment-dataset
+- Kaggle "SF Curb Ramps": https://www.kaggle.com/datasets/san-francisco/sf-curb-ramps</t>
         </is>
       </c>
       <c r="L6" s="60" t="inlineStr">
         <is>
-          <t>부분적 - TAAS(도로교통공단 교통사고분석시스템)에서 지역별·연령별 사고통계 조회 가능(대량 다운로드는 번거로움), 노인복지시설 위치는 공공데이터포털에서 확보 가능. PSI 지표 원자료 공개 여부는 미확인 → 직접 위험지수를 설계해야 할 가능성이 높음
+          <t>부분적 - TAAS(도로교통공단 교통사고분석시스템) 웹 조회 대신, 별도 Open API 포털(opendata.koroad.or.kr)에서 시군구+노인보행자 등 대상별 세분화 통계를 API로 즉시 조회 가능(회원가입+API키 발급 필요). 노인복지시설 위치는 공공데이터포털에서 확보 가능. PSI 지표 원자료 공개 여부는 미확인 → 직접 위험지수를 설계해야 할 가능성이 높음
 [데이터셋 링크]
-- TAAS 교통사고분석시스템: https://taas.koroad.or.kr/
+- KOROAD 교통사고정보 개방체계 Open API(지자체별 대상사고통계, 노인보행자 세분화 포함): https://opendata.koroad.or.kr/api/selectSttDataSet.do
+- TAAS 교통사고분석시스템(웹 조회용): https://taas.koroad.or.kr/
 - 보건복지부 노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
         </is>
       </c>
@@ -1451,14 +1456,19 @@
       </c>
       <c r="O6" s="63" t="inlineStr">
         <is>
-          <t>있음 - 9번(J열)·13번(N열) 데이터셋을 그대로 재사용, 신규 데이터 수집 없음
-[데이터셋 링크] J6·N6과 동일
+          <t>있음 - 9번·13번 모듈 데이터셋은 그대로 재사용. 다만 결합(자치구 단위 오버레이) 단계에 GIS 경계·행정코드·인구통계 3종 신규 확보 필요(이동약자_통합대시보드_기술설계.md 8절 참고)
+[결합 단계 신규 데이터 링크]
+- 자치구 GIS 경계(GeoJSON, 즉시 사용): https://github.com/datainworld/administrative_district
+- 행정표준코드(법정동코드) 조회: https://www.code.go.kr/stdcode/regCodeL.do
+- KOSIS 자치구별/1세별 인구(고령인구 비율 산출용): https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1B04006
+[모듈 데이터 링크] J6·N6과 동일
 - 장애인콜택시 일별 이용현황: https://data.seoul.go.kr/dataList/OA-13550/L/1/datasetView.do
 - 장애인콜택시 탑승내역: https://www.data.go.kr/data/15115859/fileData.do
 - 저상버스 보급현황(전국): https://www.data.go.kr/data/15106061/fileData.do
 - 서울 저상버스 노선별 보유율: https://www.data.go.kr/data/15086332/fileData.do?recommendDataYn=Y
 - AI허브 보행 안전을 위한 도로 시설물 데이터: https://www.aihub.or.kr/aihubdata/data/view.do?currMenu=115&amp;topMenu=100&amp;dataSetSn=513
 - 도로교통공단_시군구별 월별 교통사고 통계: https://www.data.go.kr/data/15070295/fileData.do
+- KOROAD 교통사고정보 개방체계 Open API(노인보행자 세분화): https://opendata.koroad.or.kr/api/selectSttDataSet.do
 - 보건복지부_노인복지 시설현황: https://www.data.go.kr/data/15039034/fileData.do</t>
         </is>
       </c>
@@ -1516,12 +1526,12 @@
       </c>
       <c r="K7" s="59" t="inlineStr">
         <is>
-          <t>AI허브 승인 필요 - 대기시간이 2일 일정에 리스크. 승인 지연 시 Roboflow/Kaggle의 sidewalk·curb-ramp 데이터로 즉시 대체 검증 필요(별도 확인 필요)</t>
+          <t>AI허브 승인 필요 - 대기시간이 2일 일정에 리스크. 승인 지연 시 Roboflow "accessibility street", Kaggle "Sidewalk Segment Dataset"/"SF Curb Ramps"로 즉시 대체 가능(검증 완료, K6 참고)</t>
         </is>
       </c>
       <c r="L7" s="60" t="inlineStr">
         <is>
-          <t>혼재 - TAAS는 웹 통계 조회 중심이라 벌크 다운로드가 번거로움. PSI 원자료 미확인은 추가 리스크</t>
+          <t>즉시(API) - TAAS 웹 조회 대신 opendata.koroad.or.kr Open API(지자체별 대상사고통계)로 대체하면 벌크 다운로드 번거로움 해소, API키 발급 절차만 필요. PSI 원자료 미확인은 여전히 리스크(자체 설계로 대응)</t>
         </is>
       </c>
       <c r="M7" s="61" t="inlineStr">
@@ -1763,12 +1773,12 @@
       </c>
       <c r="N10" s="67" t="inlineStr">
         <is>
-          <t>AI허브 승인 지연 시 Roboflow/Kaggle 대체 데이터로 CV 모듈만 축소 진행 가능. 4인이 CV팀/정형데이터팀으로 병렬 진행해도 결합 단계(지도 오버레이)에서 시간 압박 가능 - 1개 자치구로 범위를 좁히는 것을 권장. PSI 원자료는 비공개라 사고건수+연령대+노인복지시설 밀도로 자체 위험지수 설계.</t>
+          <t>AI허브 승인 지연 시 Roboflow "accessibility street", Kaggle "Sidewalk Segment Dataset"/"SF Curb Ramps"(검증 완료, K6 참고)로 CV 모듈만 축소 진행 가능. 4인이 CV팀/정형데이터팀으로 병렬 진행해도 결합 단계(지도 오버레이)에서 시간 압박 가능 - 1개 자치구로 범위를 좁히는 것을 권장. PSI 원자료는 비공개라 사고건수+연령대+노인복지시설 밀도로 자체 위험지수 설계. 사고통계는 TAAS 대신 opendata.koroad.or.kr API 사용 권장(L6 참고).</t>
         </is>
       </c>
       <c r="O10" s="68" t="inlineStr">
         <is>
-          <t>핵심은 모델을 억지로 하나로 합치지 않고 9번·13번을 독립 모듈로 유지한 채 시각화 레이어에서만 결합하는 것 - 이렇게 하면 9번의 '상' 실현성과 13번의 '중' 실현성을 각각 훼손하지 않음. 시간이 부족하면 9번(콜택시)만 완성하고 13번은 축소해도 발표 서사 손실이 적음(모듈 분리형 설계라 부분 완성도 가능). CV 모듈 승인 지연 시 13번과 동일하게 Roboflow/Kaggle 대체 데이터로 축소</t>
+          <t>핵심은 모델을 억지로 하나로 합치지 않고 9번·13번을 독립 모듈로 유지한 채 시각화 레이어에서만 결합하는 것 - 이렇게 하면 9번의 '상' 실현성과 13번의 '중' 실현성을 각각 훼손하지 않음. 시간이 부족하면 9번(콜택시)만 완성하고 13번은 축소해도 발표 서사 손실이 적음(모듈 분리형 설계라 부분 완성도 가능). CV 모듈 승인 지연 시 13번과 동일하게 Roboflow "accessibility street", Kaggle "Sidewalk Segment Dataset"/"SF Curb Ramps"(검증 완료)로 축소. 결합 단계에 필요한 GIS 경계·행정코드·인구통계 데이터는 O6 참고.</t>
         </is>
       </c>
     </row>
